--- a/models/model_comparison.xlsx
+++ b/models/model_comparison.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,18 +28,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C0006"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00006100"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -51,23 +42,8 @@
         <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -75,42 +51,25 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00BFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -478,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -550,27 +509,27 @@
           <t>non</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>max_iter=1000, solver=lbfgs (defaut)</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>0.5998</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>0.38</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="5" t="n">
         <v>0.73</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>0.21</v>
       </c>
     </row>
@@ -580,32 +539,32 @@
           <t>Regression logistique (balanced, OneVsRest)</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>balanced</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>max_iter=1000, solver=lbfgs (defaut)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>0.5192</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>0.44</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>0.63</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>0.55</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>0.38</v>
       </c>
     </row>
@@ -615,32 +574,32 @@
           <t>Regression logistique (GridSearch best, OneVsRest)</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>balanced</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>C=0.1, penalty=l2, solver=liblinear, max_iter=1000</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>0.5173</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>0.43</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>0.17</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>0.63</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="5" t="n">
         <v>0.55</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>0.38</v>
       </c>
     </row>
@@ -650,32 +609,32 @@
           <t>KNN (baseline)</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>non applicable (KNN)</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>n_neighbors=5, weights=uniform, metric=minkowski</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>0.55</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>0.44</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>0.23</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <v>0.68</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>0.33</v>
       </c>
     </row>
@@ -685,32 +644,32 @@
           <t>KNN (GridSearch best)</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>non applicable (KNN)</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>n_neighbors=14, weights=uniform, metric=chebyshev</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>0.46</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="5" t="n">
         <v>0.18</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="5" t="n">
         <v>0.73</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <v>0.54</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>0.39</v>
       </c>
     </row>
@@ -725,32 +684,102 @@
           <t>non</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>C=1, gamma=0.5, kernel=rbf</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
-        <v>0.6209</v>
-      </c>
-      <c r="E7" s="4" t="n">
+      <c r="D7" s="5" t="n">
+        <v>0.6622</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Random Forest (GridSearch best, balanced)</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=20, max_features=sqrt, min_samples_leaf=4, min_samples_split=15</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.5744</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Random Forest (sans ponderation, validation)</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=20, min_samples_leaf=4, min_samples_split=15 (sans GridSearch)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.6102</v>
+      </c>
+      <c r="E9" s="5" t="n">
         <v>0.45</v>
       </c>
-      <c r="F7" s="4" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="G7" s="4" t="n">
+      <c r="F9" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G9" s="5" t="n">
         <v>0.74</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H9" s="5" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="I7" s="4" t="n">
-        <v>0.41</v>
+      <c r="I9" s="5" t="n">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D7">
+  <conditionalFormatting sqref="D2:D9">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -762,7 +791,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E7">
+  <conditionalFormatting sqref="E2:E9">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -774,7 +803,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F7">
+  <conditionalFormatting sqref="F2:F9">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -786,7 +815,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G7">
+  <conditionalFormatting sqref="G2:G9">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -798,7 +827,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H7">
+  <conditionalFormatting sqref="H2:H9">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -810,7 +839,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I7">
+  <conditionalFormatting sqref="I2:I9">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>

--- a/models/model_comparison.xlsx
+++ b/models/model_comparison.xlsx
@@ -55,23 +55,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -437,11 +426,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
     <col width="53" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
@@ -451,7 +440,7 @@
     <col width="21" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>modele</t>
@@ -499,287 +488,357 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Regression logistique (sans ponderation, OneVsRest)</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>max_iter=1000, solver=lbfgs (defaut)</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="2" t="n">
         <v>0.5998</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="2" t="n">
         <v>0.38</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="2" t="n">
         <v>0.73</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="I2" s="5" t="n">
+      <c r="I2" s="2" t="n">
         <v>0.21</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Regression logistique (balanced, OneVsRest)</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>balanced</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>max_iter=1000, solver=lbfgs (defaut)</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="2" t="n">
         <v>0.5192</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="2" t="n">
         <v>0.17</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="2" t="n">
         <v>0.63</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="2" t="n">
         <v>0.55</v>
       </c>
-      <c r="I3" s="5" t="n">
+      <c r="I3" s="2" t="n">
         <v>0.38</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Regression logistique (GridSearch best, OneVsRest)</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>balanced</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>C=0.1, penalty=l2, solver=liblinear, max_iter=1000</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="2" t="n">
         <v>0.5173</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="2" t="n">
         <v>0.43</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="2" t="n">
         <v>0.17</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="2" t="n">
         <v>0.63</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="2" t="n">
         <v>0.55</v>
       </c>
-      <c r="I4" s="5" t="n">
+      <c r="I4" s="2" t="n">
         <v>0.38</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>KNN (baseline)</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>non applicable (KNN)</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>n_neighbors=5, weights=uniform, metric=minkowski</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="2" t="n">
         <v>0.55</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="2" t="n">
         <v>0.44</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="2" t="n">
         <v>0.23</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="2" t="n">
         <v>0.68</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="2" t="n">
         <v>0.5</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="2" t="n">
         <v>0.33</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>KNN (GridSearch best)</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>non applicable (KNN)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>n_neighbors=14, weights=uniform, metric=chebyshev</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="2" t="n">
         <v>0.6</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="2" t="n">
         <v>0.46</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="2" t="n">
         <v>0.18</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="2" t="n">
         <v>0.73</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="2" t="n">
         <v>0.54</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="2" t="n">
         <v>0.39</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KNN v2 (RandomOverSampler, baseline)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RandomOverSampler sur train</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>n_neighbors=5, weights=uniform, metric=minkowski</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KNN v2 (RandomOverSampler, GridSearch best)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RandomOverSampler sur train</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>n_neighbors=4, weights=distance, metric=minkowski</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>SVM (GridSearch best)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>non</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>C=1, gamma=0.5, kernel=rbf</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>0.6622</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="H7" s="5" t="n">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>C=10, gamma=0.1, kernel=rbf</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.6348</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Random Forest (GridSearch best, balanced)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=20, max_features=sqrt, min_samples_leaf=4, min_samples_split=15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.5744</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Random Forest (sans ponderation, validation)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>n_estimators=200, max_depth=20, min_samples_leaf=4, min_samples_split=15 (sans GridSearch)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.6102</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="H11" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="I7" s="5" t="n">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Random Forest (GridSearch best, balanced)</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>balanced</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>n_estimators=200, max_depth=20, max_features=sqrt, min_samples_leaf=4, min_samples_split=15</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>0.5744</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Random Forest (sans ponderation, validation)</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>n_estimators=200, max_depth=20, min_samples_leaf=4, min_samples_split=15 (sans GridSearch)</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>0.6102</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="I9" s="5" t="n">
+      <c r="I11" s="2" t="n">
         <v>0.39</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2:D9">
+  <conditionalFormatting sqref="D2:D11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
@@ -791,8 +850,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E9">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="E2:E11">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0.5"/>
@@ -803,8 +862,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F9">
-    <cfRule type="colorScale" priority="3">
+  <conditionalFormatting sqref="F2:F11">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0.5"/>
@@ -815,8 +874,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G9">
-    <cfRule type="colorScale" priority="4">
+  <conditionalFormatting sqref="G2:G11">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0.5"/>
@@ -827,8 +886,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H9">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="H2:H11">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0.5"/>
@@ -839,8 +898,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I9">
-    <cfRule type="colorScale" priority="6">
+  <conditionalFormatting sqref="I2:I11">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0.5"/>

--- a/models/model_comparison.xlsx
+++ b/models/model_comparison.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparaison modeles" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,8 +25,10 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -39,7 +40,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="FF305496"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,7 +64,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -135,6 +136,93 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>476249</colOff>
+      <row>12</row>
+      <rowOff>88446</rowOff>
+    </from>
+    <to>
+      <col>2</col>
+      <colOff>1311116</colOff>
+      <row>34</row>
+      <rowOff>122464</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 1"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="476249" y="2374446"/>
+          <a:ext cx="6366171" cy="4225018"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>2</col>
+      <colOff>2061483</colOff>
+      <row>11</row>
+      <rowOff>22585</rowOff>
+    </from>
+    <to>
+      <col>8</col>
+      <colOff>806903</colOff>
+      <row>41</row>
+      <rowOff>133349</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 2"/>
+        <cNvPicPr>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="7592787" y="2118085"/>
+          <a:ext cx="6481080" cy="5825764"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -426,15 +514,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="29" customWidth="1" min="2" max="2"/>
     <col width="53" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="4" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
@@ -837,6 +923,76 @@
         <v>0.39</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XGBoost (baseline, sans ponderation)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>n_estimators=100, max_depth=6, learning_rate=0.3 (defauts XGBoost)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.5979</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XGBoost (GridSearch best, balanced)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>balanced (sample_weight)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>n_estimators=400, max_depth=4, learning_rate=0.05, subsample=0.8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.5397999999999999</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D11">
     <cfRule type="colorScale" priority="1">
@@ -844,72 +1000,73 @@
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0.5"/>
         <cfvo type="num" val="1"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E11">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0.5"/>
         <cfvo type="num" val="1"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F11">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0.5"/>
         <cfvo type="num" val="1"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G11">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0.5"/>
         <cfvo type="num" val="1"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H11">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0.5"/>
         <cfvo type="num" val="1"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I11">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="0.5"/>
         <cfvo type="num" val="1"/>
-        <color rgb="00F8696B"/>
-        <color rgb="00FFEB84"/>
-        <color rgb="0063BE7B"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>